--- a/artfynd/A 8064-2026 artfynd.xlsx
+++ b/artfynd/A 8064-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135644127</v>
       </c>
       <c r="B2" t="n">
-        <v>97479</v>
+        <v>97506</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135643309</v>
       </c>
       <c r="B3" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135643812</v>
       </c>
       <c r="B4" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8064-2026 artfynd.xlsx
+++ b/artfynd/A 8064-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135644127</v>
       </c>
       <c r="B2" t="n">
-        <v>97511</v>
+        <v>97513</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135643309</v>
       </c>
       <c r="B3" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135643812</v>
       </c>
       <c r="B4" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8064-2026 artfynd.xlsx
+++ b/artfynd/A 8064-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135644127</v>
       </c>
       <c r="B2" t="n">
-        <v>97513</v>
+        <v>97530</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135643309</v>
       </c>
       <c r="B3" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135643812</v>
       </c>
       <c r="B4" t="n">
-        <v>92050</v>
+        <v>92064</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135644316</v>
       </c>
       <c r="B5" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>135657406</v>
       </c>
       <c r="B6" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>135642631</v>
       </c>
       <c r="B7" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>135643779</v>
       </c>
       <c r="B8" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>135793362</v>
       </c>
       <c r="B9" t="n">
-        <v>57980</v>
+        <v>57982</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>135793461</v>
       </c>
       <c r="B10" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 8064-2026 artfynd.xlsx
+++ b/artfynd/A 8064-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135644127</v>
       </c>
       <c r="B2" t="n">
-        <v>97530</v>
+        <v>97531</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135643309</v>
       </c>
       <c r="B3" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135643812</v>
       </c>
       <c r="B4" t="n">
-        <v>92064</v>
+        <v>92065</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8064-2026 artfynd.xlsx
+++ b/artfynd/A 8064-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135644127</v>
       </c>
       <c r="B2" t="n">
-        <v>97531</v>
+        <v>97532</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135643309</v>
       </c>
       <c r="B3" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135643812</v>
       </c>
       <c r="B4" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 8064-2026 artfynd.xlsx
+++ b/artfynd/A 8064-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135644127</v>
       </c>
       <c r="B2" t="n">
-        <v>97532</v>
+        <v>97533</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135643309</v>
       </c>
       <c r="B3" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135643812</v>
       </c>
       <c r="B4" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135644316</v>
       </c>
       <c r="B5" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>135657406</v>
       </c>
       <c r="B6" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>135642631</v>
       </c>
       <c r="B7" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>135643779</v>
       </c>
       <c r="B8" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>135793362</v>
       </c>
       <c r="B9" t="n">
-        <v>57982</v>
+        <v>57983</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>135793461</v>
       </c>
       <c r="B10" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 8064-2026 artfynd.xlsx
+++ b/artfynd/A 8064-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135644127</v>
       </c>
       <c r="B2" t="n">
-        <v>97533</v>
+        <v>97539</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>135643309</v>
       </c>
       <c r="B3" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>135643812</v>
       </c>
       <c r="B4" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>135644316</v>
       </c>
       <c r="B5" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>135657406</v>
       </c>
       <c r="B6" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>135642631</v>
       </c>
       <c r="B7" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>135643779</v>
       </c>
       <c r="B8" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>135793362</v>
       </c>
       <c r="B9" t="n">
-        <v>57983</v>
+        <v>57987</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>135793461</v>
       </c>
       <c r="B10" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 8064-2026 artfynd.xlsx
+++ b/artfynd/A 8064-2026 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>135644316</v>
       </c>
       <c r="B5" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>135657406</v>
       </c>
       <c r="B6" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>135642631</v>
       </c>
       <c r="B7" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>135643779</v>
       </c>
       <c r="B8" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>135793362</v>
       </c>
       <c r="B9" t="n">
-        <v>57987</v>
+        <v>57988</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>135793461</v>
       </c>
       <c r="B10" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 8064-2026 artfynd.xlsx
+++ b/artfynd/A 8064-2026 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>135644316</v>
       </c>
       <c r="B5" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>135657406</v>
       </c>
       <c r="B6" t="n">
-        <v>57985</v>
+        <v>57990</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>135642631</v>
       </c>
       <c r="B7" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>135643779</v>
       </c>
       <c r="B8" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>135793362</v>
       </c>
       <c r="B9" t="n">
-        <v>57988</v>
+        <v>57993</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>135793461</v>
       </c>
       <c r="B10" t="n">
-        <v>57175</v>
+        <v>57180</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 8064-2026 artfynd.xlsx
+++ b/artfynd/A 8064-2026 artfynd.xlsx
@@ -1019,7 +1019,7 @@
         <v>135644316</v>
       </c>
       <c r="B5" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1136,7 +1136,7 @@
         <v>135657406</v>
       </c>
       <c r="B6" t="n">
-        <v>57990</v>
+        <v>58003</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>135642631</v>
       </c>
       <c r="B7" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1364,7 +1364,7 @@
         <v>135643779</v>
       </c>
       <c r="B8" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1481,7 +1481,7 @@
         <v>135793362</v>
       </c>
       <c r="B9" t="n">
-        <v>57993</v>
+        <v>58006</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1606,7 +1606,7 @@
         <v>135793461</v>
       </c>
       <c r="B10" t="n">
-        <v>57180</v>
+        <v>57193</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
